--- a/CompanyData.xlsx
+++ b/CompanyData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Web_MKPD_Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550355F7-62FA-493B-A4AF-3B98D605638F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E62CCDA-52FD-4EC6-BB0D-C57218663047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>Company Name</t>
   </si>
@@ -110,13 +110,25 @@
   </si>
   <si>
     <t>WAHOO POOL &amp; LANDSCAPE CONSTRUCTION PTY. LTD.</t>
+  </si>
+  <si>
+    <t>JUSTSPAS WOLLON PTY LTD</t>
+  </si>
+  <si>
+    <t>JUSTSPAS WOLLON PTY LTD_34669379177</t>
+  </si>
+  <si>
+    <t>28 Swan St, Wollongong NSW 2500</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,6 +140,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF474747"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -165,11 +183,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -472,15 +492,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="61.21875" customWidth="1"/>
-    <col min="7" max="7" width="70.33203125" customWidth="1"/>
-    <col min="8" max="8" width="23.44140625" customWidth="1"/>
+    <col min="1" max="1" width="61.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="51.85546875" customWidth="1"/>
+    <col min="6" max="6" width="52.7109375" customWidth="1"/>
+    <col min="7" max="7" width="56.42578125" customWidth="1"/>
+    <col min="8" max="8" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,11 +531,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C2">
@@ -532,11 +557,11 @@
         <v>1308749</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C3">
@@ -558,11 +583,11 @@
         <v>15445275</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C4">
@@ -584,11 +609,11 @@
         <v>15247996</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C5">
@@ -605,6 +630,29 @@
       </c>
       <c r="G5" t="s">
         <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45118</v>
+      </c>
+      <c r="C6">
+        <v>34669379177</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/CompanyData.xlsx
+++ b/CompanyData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E62CCDA-52FD-4EC6-BB0D-C57218663047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BED46CE-F064-4B6D-AE29-16C78D7D0262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>Company Name</t>
   </si>
@@ -110,15 +110,6 @@
   </si>
   <si>
     <t>WAHOO POOL &amp; LANDSCAPE CONSTRUCTION PTY. LTD.</t>
-  </si>
-  <si>
-    <t>JUSTSPAS WOLLON PTY LTD</t>
-  </si>
-  <si>
-    <t>JUSTSPAS WOLLON PTY LTD_34669379177</t>
-  </si>
-  <si>
-    <t>28 Swan St, Wollongong NSW 2500</t>
   </si>
   <si>
     <t>-</t>
@@ -632,28 +623,11 @@
         <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="2">
-        <v>45118</v>
-      </c>
-      <c r="C6">
-        <v>34669379177</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" t="s">
-        <v>33</v>
-      </c>
+      <c r="F6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
